--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260604.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260604.xlsx
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>99,386,635</t>
+          <t>76,975,827</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>76,975,827</t>
+          <t>99,386,635</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>202606NYF</t>
+          <t>6919</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>台灣50ETF股票期貨</t>
+          <t>康霈*</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>1,738</t>
+          <t>19,447,059</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>6919</t>
+          <t>202606NYF</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>康霈*</t>
+          <t>台灣50ETF股票期貨</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>19,447,059</t>
+          <t>1,738</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
